--- a/output/full_scan/batch_seq0_2026-08-31.xlsx
+++ b/output/full_scan/batch_seq0_2026-08-31.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8080</v>
+        <v>8431</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>847.0297480032733</v>
+        <v>981.6256953991348</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>29</v>
+        <v>53.6</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>62.9478908450053</v>
+        <v>64.29183732162238</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>53.41901936600826</v>
+        <v>14.7110642692974</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.87807626309368</v>
+        <v>3.762569539913462</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0762257042117863</v>
+        <v>0.7456863201686686</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8431</v>
+        <v>8103</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>781.6256953991347</v>
+        <v>968.887712658112</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>53.6</v>
+        <v>119</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.29183731792227</v>
+        <v>75.70397206648373</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14.71106426105382</v>
+        <v>37.30714111100423</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.762569539913462</v>
+        <v>0.9887712658112062</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.7456863200828082</v>
+        <v>4.008387937921687</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8111</v>
+        <v>8080</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>735.9830555687788</v>
+        <v>962.0297480032732</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.26028999717612</v>
+        <v>62.94788505768485</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20.07387216977074</v>
+        <v>53.41901938794468</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.761438292132987</v>
+        <v>1.87807626309368</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.6499403420261445</v>
+        <v>0.076225704116387</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8147</v>
+        <v>8111</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>680.1141627236943</v>
+        <v>905.9830555687788</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>131</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.09501421539681</v>
+        <v>63.26029005708424</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24.55257617914173</v>
+        <v>20.07387225309291</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.024126430662029</v>
+        <v>1.761438292132987</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.535284404636427</v>
+        <v>0.6499403418353484</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8103</v>
+        <v>8147</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>658.887712658112</v>
+        <v>850.1141627236937</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>75.70397213953575</v>
+        <v>57.09501433490675</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>37.30714108831116</v>
+        <v>24.55257619631361</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9887712658112062</v>
+        <v>2.024126430662029</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,11 +782,11 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.008387938085178</v>
+        <v>1.535284404159447</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>604.5028832686791</v>
+        <v>804.518923943518</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>540</v>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>69.04072447343538</v>
+        <v>69.04072448039766</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.83578645862972</v>
+        <v>23.83578647953535</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.723266937506639</v>
+        <v>1.727433921158376</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>19.49253007535825</v>
+        <v>19.49253007552992</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>9105</v>
+        <v>8155</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>593.9365744576277</v>
+        <v>776.9350068122568</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>365</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.20063482150693</v>
+        <v>64.37371291021533</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16.29057794965457</v>
+        <v>22.35010548799748</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.482034988981942</v>
+        <v>1.271139811494311</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.036745086419967</v>
+        <v>7.883922336922158</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, williams_r_recovery, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8155</v>
+        <v>8240</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>576.9350068122535</v>
+        <v>776.038610793252</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>365</v>
+        <v>47.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.37371289504834</v>
+        <v>63.08872706520724</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.35010542497878</v>
+        <v>25.45184825384618</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.271139811494311</v>
+        <v>3.148865099066693</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>7.883922337112938</v>
+        <v>0.8440673837868331</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8240</v>
+        <v>9105</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>576.0386107932519</v>
+        <v>718.9365744576277</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>47.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.08872704566983</v>
+        <v>57.20063486579374</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25.45184821559337</v>
+        <v>16.29057801773608</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.148865099066693</v>
+        <v>1.482034988981942</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.8440673838345281</v>
+        <v>0.0367450863970729</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, williams_r_recovery, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8299</v>
+        <v>8215</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>554.6088842135324</v>
+        <v>666.8890954159535</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2165</v>
+        <v>25.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>56.99937610715103</v>
+        <v>55.01691920977731</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>12.74847349890704</v>
+        <v>25.12682090963354</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.873317560215965</v>
+        <v>1.765056827852619</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>18.01466267958069</v>
+        <v>0.2842133560291052</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8093</v>
+        <v>8085</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>548.8470850168501</v>
+        <v>615.6144972719745</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28.05</v>
+        <v>15.85</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.23887924292968</v>
+        <v>80.57696651319407</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18.40323157414602</v>
+        <v>28.53184905956909</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5469267972068791</v>
+        <v>1.161449727197452</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.3325723141436616</v>
+        <v>0.487587895692378</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8443</v>
+        <v>8046</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>539.3793238843766</v>
+        <v>595.5259297107765</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11.35</v>
+        <v>1230</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45.49775720704122</v>
+        <v>54.94414814370317</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>42.54970291058328</v>
+        <v>11.17269383811359</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.0851084928379751</v>
+        <v>1.868482573050652</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.0136003393390104</v>
+        <v>2.783298845819097</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8215</v>
+        <v>8299</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>526.8890954159535</v>
+        <v>560.9740561031704</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>25.6</v>
+        <v>2165</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.01691920486196</v>
+        <v>56.99937611915561</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>25.12682084362817</v>
+        <v>12.74847354542138</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.765056827852619</v>
+        <v>3.298392878224328</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.2842133560672631</v>
+        <v>18.01466267919892</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8271</v>
+        <v>8093</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>521.7494474248278</v>
+        <v>548.8470850168501</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>227.5</v>
+        <v>28.05</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>51.98477271087859</v>
+        <v>61.23887924292968</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.57657166446974</v>
+        <v>18.4032315549429</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4135945658570702</v>
+        <v>0.5469267972068791</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.127728710452456</v>
+        <v>0.3325723141763608</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8473</v>
+        <v>8086</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>517.136780105446</v>
+        <v>542.4020495351784</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45.9</v>
+        <v>118</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.23627089135787</v>
+        <v>48.97218204361389</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24.1282971637969</v>
+        <v>21.01567031691189</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4642732315116751</v>
+        <v>1.37481572153162</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2879217729054227</v>
+        <v>1.148318483923752</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8367</v>
+        <v>8443</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>501.9129309076813</v>
+        <v>539.3793238843766</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>40.7</v>
+        <v>11.35</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>53.41554421933502</v>
+        <v>45.4977571626312</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>27.83173106992944</v>
+        <v>42.54970292763053</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4657887008967901</v>
+        <v>0.0851084928379751</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0325873252468112</v>
+        <v>-0.0136003393390104</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8442</v>
+        <v>8473</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>501.7037442768667</v>
+        <v>517.136780105446</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45.3</v>
+        <v>45.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>50.30612159198273</v>
+        <v>56.2362709433643</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20.55192374667593</v>
+        <v>24.12829714173889</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.246382549236676</v>
+        <v>0.4642732315116751</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.0117503889736345</v>
+        <v>0.2879217728386439</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>9912</v>
+        <v>8213</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>469.7428046650471</v>
+        <v>504.8037101070759</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>12.9</v>
+        <v>32.9</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>50.45293781547571</v>
+        <v>52.74337495175648</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>17.38491542310977</v>
+        <v>20.78394344443891</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.489535473009296</v>
+        <v>0.8335456522116321</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0579937626599109</v>
+        <v>0.1559359852319367</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8289</v>
+        <v>8043</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>466.3219925867457</v>
+        <v>503.9562057959903</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45.5</v>
+        <v>142.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45.68482670706552</v>
+        <v>49.7863693169237</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18.61484039403392</v>
+        <v>15.11149616616037</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4172691340609085</v>
+        <v>0.7712706727008364</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.436098098989542</v>
+        <v>1.358930010389474</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8932</v>
+        <v>8367</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>461.5331424646718</v>
+        <v>501.9129309076813</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>96</v>
+        <v>40.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>41.13389785223802</v>
+        <v>53.41554372687258</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.10952371322142</v>
+        <v>27.83173108858176</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.04976183787316</v>
+        <v>0.4657887008967901</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.9585628201564028</v>
+        <v>0.0325873251991104</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8422</v>
+        <v>8271</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>452.2414684597224</v>
+        <v>501.7494474248279</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>26.8</v>
+        <v>227.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.66032919466859</v>
+        <v>51.98477271571477</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>12.99514164967923</v>
+        <v>24.57657176460246</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.514115955133674</v>
+        <v>0.4135945658570702</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0521376096041417</v>
+        <v>-1.127728710643245</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>9905</v>
+        <v>8442</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>450.5715529335296</v>
+        <v>501.7037442768668</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>21.5</v>
+        <v>45.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>60.08603773133354</v>
+        <v>50.30612157205137</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.56037276662065</v>
+        <v>20.551923752443</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3521389742231802</v>
+        <v>1.246382549236676</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.0002897346022779</v>
+        <v>-0.0117503890117908</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8171</v>
+        <v>8249</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>430.5926737744005</v>
+        <v>492.7736288103531</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>20.3</v>
+        <v>41.6</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.09343832057671</v>
+        <v>46.8900565288213</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>13.10156064615144</v>
+        <v>22.62248530821735</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.171763773469205</v>
+        <v>0.4145474813627813</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.125401223014366</v>
+        <v>0.3038965262711115</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8046</v>
+        <v>8438</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>425.5259297107767</v>
+        <v>490.4000355779968</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1230</v>
+        <v>71.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>54.94414813415412</v>
+        <v>55.08702565448917</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11.17269370591988</v>
+        <v>19.36357150118201</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.868482573050652</v>
+        <v>0.7542160465545947</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.783298845532734</v>
+        <v>1.435848293219931</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8222</v>
+        <v>8422</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>421.5454843110882</v>
+        <v>472.2414684597224</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>39.1</v>
+        <v>26.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>50.47808675546762</v>
+        <v>50.66032919466859</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>25.29838314420641</v>
+        <v>12.99514157352899</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4720053637922871</v>
+        <v>1.514115955133674</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0168687290801443</v>
+        <v>0.0521376096041417</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8105</v>
+        <v>9912</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>418.9509456785741</v>
+        <v>469.7428046650471</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>16.1</v>
+        <v>12.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46.60925156731945</v>
+        <v>50.45293779380245</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.97660008617609</v>
+        <v>17.38491542774913</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.534659517215826</v>
+        <v>2.489535473009296</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0944525644088316</v>
+        <v>0.05799376267899</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8462</v>
+        <v>8289</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>416.1482309126213</v>
+        <v>466.3219925867457</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>168</v>
+        <v>45.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>47.57366086202236</v>
+        <v>45.68482671095328</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>37.90408086437722</v>
+        <v>18.61484050371283</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.324880641885543</v>
+        <v>0.4172691340609085</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.415480087991515</v>
+        <v>0.4360980989323025</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8085</v>
+        <v>8932</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>415.6144972719745</v>
+        <v>461.5331424646718</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>15.85</v>
+        <v>96</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>80.57696645841918</v>
+        <v>41.13389790010898</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.53184905178868</v>
+        <v>14.10952373295405</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.161449727197452</v>
+        <v>1.04976183787316</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.4875878957305363</v>
+        <v>-0.9585628201564028</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8182</v>
+        <v>8162</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>415.2750732076144</v>
+        <v>456.4269067308345</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>40.15</v>
+        <v>62.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>47.2353662575063</v>
+        <v>53.35515149134271</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>9.300730564664049</v>
+        <v>19.44621011138937</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3699534852527653</v>
+        <v>0.6525173192307527</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2903176608347808</v>
+        <v>1.148750602591569</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8109</v>
+        <v>9905</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>415.0961197779558</v>
+        <v>450.5715529335296</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>129</v>
+        <v>21.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>48.28944899483591</v>
+        <v>60.08603771021394</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.698587730804</v>
+        <v>18.56037266120904</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4366361177661599</v>
+        <v>0.3521389742231802</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.15306425013788</v>
+        <v>-0.0002897345927385</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9930</v>
+        <v>8102</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>410.7663591471298</v>
+        <v>438.8897421188802</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>63</v>
+        <v>67.2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45.08296187325308</v>
+        <v>50.94671704124185</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>29.265864843572</v>
+        <v>9.935418710284075</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8350030742330465</v>
+        <v>0.1107578312919903</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.106048476582115</v>
+        <v>0.6238686592433536</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8482</v>
+        <v>8464</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>410.1642179149106</v>
+        <v>438.2005227645198</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>46.3</v>
+        <v>374</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>48.86355866867773</v>
+        <v>51.95746995124377</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3.745696502807417</v>
+        <v>19.76274864701418</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9505536536122292</v>
+        <v>0.6364245645926865</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1676116081242235</v>
+        <v>-1.218962447074152</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8086</v>
+        <v>8171</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>402.4020495351783</v>
+        <v>430.5926737744007</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118</v>
+        <v>20.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>48.9721820242928</v>
+        <v>55.09343846214091</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.01567026045681</v>
+        <v>13.1015606908102</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.37481572153162</v>
+        <v>2.171763773469205</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.148318484000064</v>
+        <v>0.1254012229380476</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8423</v>
+        <v>8222</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>401.6260238061843</v>
+        <v>421.5454843110882</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>17.85</v>
+        <v>39.1</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.11529953803298</v>
+        <v>50.47808680670369</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.30893630280713</v>
+        <v>25.29838330232045</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6268656716417911</v>
+        <v>0.4720053637922871</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0050404267644868</v>
+        <v>-0.016868729251858</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8440</v>
+        <v>8105</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>399.2753230160591</v>
+        <v>418.9509456785741</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>20.35</v>
+        <v>16.1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.53464317103485</v>
+        <v>46.60925158243789</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>22.49652338140431</v>
+        <v>25.97660008617608</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3806121666538868</v>
+        <v>2.534659517215826</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0962212031132883</v>
+        <v>0.0944525643482772</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8213</v>
+        <v>8462</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>394.8037101070759</v>
+        <v>416.1482309126213</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>32.9</v>
+        <v>168</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.74337488093941</v>
+        <v>47.57366087339869</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.7839433634188</v>
+        <v>37.90408088845187</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8335456522116321</v>
+        <v>1.324880641885543</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1559359853273382</v>
+        <v>-1.415480087991515</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9103</v>
+        <v>8182</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>389.9662334036721</v>
+        <v>415.2750732076144</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>5.13</v>
+        <v>40.15</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46.95303277021054</v>
+        <v>47.23536628110595</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10.38955059178102</v>
+        <v>9.300730578376289</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6296975606632776</v>
+        <v>0.3699534852527653</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0074049881934445</v>
+        <v>0.2903176608157056</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8926</v>
+        <v>8109</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>382.7704001289895</v>
+        <v>415.0961197779557</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>55.9</v>
+        <v>129</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>36.08578058434502</v>
+        <v>48.28944900149756</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31.10154334300399</v>
+        <v>16.698587730804</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.013934307452368</v>
+        <v>0.4366361177661599</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3952284524209011</v>
+        <v>-0.15306425013788</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8249</v>
+        <v>9930</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>377.7736288103531</v>
+        <v>410.7663591471298</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>41.6</v>
+        <v>63</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46.89005652169413</v>
+        <v>45.0829617142172</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.6224854147629</v>
+        <v>29.26586496871875</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4145474813627813</v>
+        <v>0.8350030742330465</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.3038965263092716</v>
+        <v>0.1060484766965886</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8940</v>
+        <v>8482</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>368.4171373365041</v>
+        <v>410.1642179149107</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>15.3</v>
+        <v>46.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>43.68486254122551</v>
+        <v>48.86355868825062</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13.43518891456238</v>
+        <v>3.745696519672464</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.030980571506005</v>
+        <v>0.9505536536122292</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0268957190945917</v>
+        <v>-0.1676116083150153</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8054</v>
+        <v>8227</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>367.1369380329249</v>
+        <v>410.0321406772832</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>156.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>44.79899214374875</v>
+        <v>49.7610176648527</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.92477256337446</v>
+        <v>17.40149417783873</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7673073194877389</v>
+        <v>0.5935068609470867</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.040216139217698</v>
+        <v>1.96269349233368</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8234</v>
+        <v>8423</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>366.989348667664</v>
+        <v>401.6260238061843</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>17.85</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.92025515972027</v>
+        <v>51.11529951628191</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>18.59097364490972</v>
+        <v>17.30893638455763</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3850370886395006</v>
+        <v>0.6268656716417911</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0772213179316978</v>
+        <v>-0.0050404267549463</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8110</v>
+        <v>8440</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>366.3268933786387</v>
+        <v>399.2753230160591</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>45.65</v>
+        <v>20.35</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>50.6680779690573</v>
+        <v>51.53464305053248</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>9.22502513705037</v>
+        <v>22.49652338269964</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4293851564924512</v>
+        <v>0.3806121666538868</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.3140871323173179</v>
+        <v>0.09622120309420951</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8411</v>
+        <v>9103</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>365.3755516138266</v>
+        <v>389.9662334036721</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>13</v>
+        <v>5.13</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.82730726226499</v>
+        <v>46.95303283902196</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>14.19749199433205</v>
+        <v>10.38955059197456</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.160909197561807</v>
+        <v>0.6296975606632776</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0146911796162393</v>
+        <v>-0.0074049882029847</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8390</v>
+        <v>8926</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>365.2662153365508</v>
+        <v>382.7704001289895</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>99.2</v>
+        <v>55.9</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.51593721478313</v>
+        <v>36.08578055488962</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14.62974386543382</v>
+        <v>31.10154330833007</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6848592697693751</v>
+        <v>1.013934307452368</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.4437912935518284</v>
+        <v>0.3952284524113532</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8043</v>
+        <v>8940</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>363.9562057959902</v>
+        <v>368.4171373365041</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>142.5</v>
+        <v>15.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.78636931245426</v>
+        <v>43.68486254122551</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.11149615478056</v>
+        <v>13.43518890827477</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7712706727008364</v>
+        <v>3.030980571506005</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.358930010418099</v>
+        <v>0.0268957190850508</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8374</v>
+        <v>8054</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>352.3316896478397</v>
+        <v>367.136938032925</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>81</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.82731997155356</v>
+        <v>44.79899182374951</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15.82778022879256</v>
+        <v>16.92477251228766</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3121079748546802</v>
+        <v>0.7673073194877389</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0407578381851212</v>
+        <v>1.040216140267071</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8096</v>
+        <v>8234</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>350.4290261921096</v>
+        <v>366.9893486676639</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>109</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>39.50798281054503</v>
+        <v>51.92025515327938</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>22.93525279676124</v>
+        <v>18.59097368469418</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.3123090219265553</v>
+        <v>0.3850370886395006</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>1</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2794979059662923</v>
+        <v>-0.0772213177981397</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8438</v>
+        <v>8110</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>350.4000355779968</v>
+        <v>366.3268933786387</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>71.7</v>
+        <v>45.65</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>55.08702562795309</v>
+        <v>50.66807797903632</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.36357138658663</v>
+        <v>9.225025130459166</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7542160465545947</v>
+        <v>0.4293851564924512</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.435848293286712</v>
+        <v>0.3140871322886908</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8261</v>
+        <v>8411</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>344.5520250149131</v>
+        <v>365.3755516138266</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>178.5</v>
+        <v>13</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>42.70749867910765</v>
+        <v>54.82730719273264</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.36259360045256</v>
+        <v>14.19749201699596</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3734762712631119</v>
+        <v>1.160909197561807</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.298458517142089</v>
+        <v>-0.0146911796162393</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8162</v>
+        <v>8390</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>341.4269067308344</v>
+        <v>365.2662153365508</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>62.5</v>
+        <v>99.2</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.35515145928387</v>
+        <v>50.51593725502944</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.44621010959869</v>
+        <v>14.6297438578773</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6525173192307527</v>
+        <v>0.6848592697693751</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.148750602772827</v>
+        <v>0.4437912935899887</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8131</v>
+        <v>8404</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>337.8810976109653</v>
+        <v>358.4430492434308</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>63.7</v>
+        <v>16.25</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.28500839949778</v>
+        <v>46.75043927801397</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>7.279398180493644</v>
+        <v>13.31237562894328</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3957116924431753</v>
+        <v>1.464644175283131</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.3527813532512549</v>
+        <v>0.0333522981982714</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8996</v>
+        <v>8374</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>325.4982033079688</v>
+        <v>352.3316896478395</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1175</v>
+        <v>81</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.15522471412561</v>
+        <v>47.82732001745803</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>19.40977398692954</v>
+        <v>15.82778026136514</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9723672540202788</v>
+        <v>0.3121079748546802</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>12.46150800269816</v>
+        <v>-0.0407578382996061</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>9904</v>
+        <v>8074</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>324.5375392881867</v>
+        <v>352.1685523835359</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>24.85</v>
+        <v>55.9</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.54947148666372</v>
+        <v>48.78029709195758</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.98298499002835</v>
+        <v>16.39254010718357</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.000943189793604</v>
+        <v>0.951584795089903</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0378865802265825</v>
+        <v>0.5989445747036786</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8464</v>
+        <v>8096</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>323.20052276452</v>
+        <v>350.4290261921095</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>374</v>
+        <v>109</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.95746984941421</v>
+        <v>39.50798280522756</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.7627485737282</v>
+        <v>22.93525281460632</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6364245645926865</v>
+        <v>0.3123090219265553</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-1.218962445833957</v>
+        <v>0.279497906004452</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8481</v>
+        <v>8261</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>322.1858354696247</v>
+        <v>344.5520250149131</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>40.8</v>
+        <v>178.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.1145928781856</v>
+        <v>42.70749871006985</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12.1923908243108</v>
+        <v>15.36259380298521</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3520660039223642</v>
+        <v>0.3734762712631119</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.07260512766977879</v>
+        <v>2.298458516474309</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8097</v>
+        <v>8131</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>316.9293593102511</v>
+        <v>337.8810976109653</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>49.2</v>
+        <v>63.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>31.04404911322584</v>
+        <v>49.28500840680818</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>26.49629311894047</v>
+        <v>7.279398185854599</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.403173874710737</v>
+        <v>0.3957116924431753</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0462284764629536</v>
+        <v>0.3527813531749286</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8429</v>
+        <v>8996</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>313.4226338072191</v>
+        <v>325.4982033079687</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>6.01</v>
+        <v>1175</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.27957609638885</v>
+        <v>51.15522472354764</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9.162326326127994</v>
+        <v>19.40977407609339</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5343264549237028</v>
+        <v>0.9723672540202788</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0086284515992341</v>
+        <v>12.46150800327068</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8101</v>
+        <v>9904</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>311.6295817507979</v>
+        <v>324.5375392881867</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>12.4</v>
+        <v>24.85</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,49 +3626,49 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.12102104606424</v>
+        <v>53.54947158878876</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>8.562589379757247</v>
+        <v>18.98298497523408</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.0709971796045539</v>
+        <v>1.000943189793604</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2599782743898671</v>
+        <v>0.0378865800644102</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8163</v>
+        <v>8481</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>307.0043137329109</v>
+        <v>322.1858354696247</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>31.1</v>
+        <v>40.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.51335281261921</v>
+        <v>49.11459272418678</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.93736301541836</v>
+        <v>12.19239080489446</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6114251304395448</v>
+        <v>0.3520660039223642</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2429590690945657</v>
+        <v>0.07260512778425469</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>9955</v>
+        <v>8097</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>300.4652169649262</v>
+        <v>316.9293593102511</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>24.2</v>
+        <v>49.2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.92698732683105</v>
+        <v>31.04404925596408</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.44294745136805</v>
+        <v>26.49629303481132</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7778028462592084</v>
+        <v>1.403173874710737</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0608809042495542</v>
+        <v>0.0462284763484759</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8227</v>
+        <v>8064</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>295.0321406772831</v>
+        <v>316.0713391728775</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>156.5</v>
+        <v>100</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.76101765601014</v>
+        <v>43.94722880817776</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17.40149418197758</v>
+        <v>16.98215346171714</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5935068609470867</v>
+        <v>0.7587928486163047</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>1.962693492524472</v>
+        <v>1.266201325152896</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8176</v>
+        <v>8429</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>291.9445610879508</v>
+        <v>313.4226338072191</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>6.01</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46.99820835708535</v>
+        <v>43.2795762515078</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.98400394449176</v>
+        <v>9.162326393150169</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7336657862740158</v>
+        <v>0.5343264549237028</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0077975225468413</v>
+        <v>0.008628451578246699</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8463</v>
+        <v>8101</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>284.4608771245489</v>
+        <v>311.6295817507979</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>21.4</v>
+        <v>12.4</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.43672769937822</v>
+        <v>51.1210210232661</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>16.51390378898335</v>
+        <v>8.562589416884547</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7828789357892353</v>
+        <v>0.0709971796045539</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.048576288830965</v>
+        <v>0.2599782744184873</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8081</v>
+        <v>8163</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>279.1370924135061</v>
+        <v>307.0043137329109</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>255.5</v>
+        <v>31.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.28337426901744</v>
+        <v>42.51335289671962</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16.26344944723419</v>
+        <v>16.93736301541837</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5720623552472773</v>
+        <v>0.6114251304395448</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.7651776996104873</v>
+        <v>0.2429590689991697</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8150</v>
+        <v>9955</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>278.8968328344329</v>
+        <v>300.4652169649262</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>24.2</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.19556610719857</v>
+        <v>44.92698732683105</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.802512359351445</v>
+        <v>20.44294744347144</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4435081012310461</v>
+        <v>0.7778028462592084</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.5343242957321404</v>
+        <v>0.0608809042590914</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8071</v>
+        <v>8176</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>278.6154125204008</v>
+        <v>291.9445610879508</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>24.05</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.36536854621964</v>
+        <v>46.9982084137334</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.00356497414117</v>
+        <v>16.98400396694904</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3738677508190254</v>
+        <v>0.7336657862740158</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1539571175715783</v>
+        <v>-0.0077975225563805</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8050</v>
+        <v>8463</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>273.4806693598576</v>
+        <v>284.4608771245489</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>56.1</v>
+        <v>21.4</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.91352839595795</v>
+        <v>53.43672771775898</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10.53974852583219</v>
+        <v>16.51390391838649</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.1936839649119759</v>
+        <v>0.7828789357892353</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.3758279303627186</v>
+        <v>0.048576288830965</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8488</v>
+        <v>9802</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>272.8513017482661</v>
+        <v>280.7106098990532</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>9.92</v>
+        <v>71.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.11589206751971</v>
+        <v>46.75115058109144</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19.0157411222063</v>
+        <v>9.996714884115132</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.0195766452579736</v>
+        <v>0.2354982235889754</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.009274110125283499</v>
+        <v>0.1512200151868039</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>9902</v>
+        <v>8071</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>268.6202080597382</v>
+        <v>278.6154125204008</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13.7</v>
+        <v>24.05</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.21214981957903</v>
+        <v>49.3653685339425</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.236959491867207</v>
+        <v>14.00356500542458</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7252493849020475</v>
+        <v>0.3738677508190254</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0104644398693154</v>
+        <v>0.1539571175715783</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8454</v>
+        <v>8050</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>264.9084277937239</v>
+        <v>273.4806693598576</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>247</v>
+        <v>56.1</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.2541460272553</v>
+        <v>43.91352847541066</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.7113969079339</v>
+        <v>10.53974848069822</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4609438419742498</v>
+        <v>0.1936839649119759</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.585759621380336</v>
+        <v>-0.3758279305725965</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8104</v>
+        <v>8488</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>263.5268279754024</v>
+        <v>272.8513017482661</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>30.85</v>
+        <v>9.92</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>42.08769587528904</v>
+        <v>49.11589552254515</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>24.86180437817396</v>
+        <v>19.01574109260048</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8103441218517906</v>
+        <v>0.0195766452579736</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.2639887938753532</v>
+        <v>-0.009274110125283499</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8112</v>
+        <v>8081</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>261.1905856556352</v>
+        <v>269.1370924135061</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>90.8</v>
+        <v>255.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,25 +4368,25 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.47077882855562</v>
+        <v>46.28337426901744</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11.52581196368694</v>
+        <v>16.2634494884004</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3179246151727883</v>
+        <v>0.5720623552472773</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.4005302059663511</v>
+        <v>0.7651777000874853</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8210</v>
+        <v>8150</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>258.6400165156093</v>
+        <v>268.8968328344329</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>969</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,25 +4421,25 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>41.49586134111709</v>
+        <v>48.19556611082218</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.98765841855216</v>
+        <v>9.802512360537932</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6768379287720402</v>
+        <v>0.4435081012310461</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>3.649158598397989</v>
+        <v>0.5343242957798326</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8091</v>
+        <v>9902</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>258.0575571367409</v>
+        <v>268.6202080597383</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>217.5</v>
+        <v>13.7</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.80763719914678</v>
+        <v>48.21214958342225</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.22100861364462</v>
+        <v>8.236959507516364</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.9696094029314486</v>
+        <v>0.7252493849020475</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.5392930164595233</v>
+        <v>-0.0104644398597761</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8114</v>
+        <v>8454</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>256.9103929573737</v>
+        <v>264.9084277937239</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>39.67616503974455</v>
+        <v>40.25414606257568</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.12409263051949</v>
+        <v>10.71139686925916</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6430788762410677</v>
+        <v>0.4609438419742498</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.461033814007721</v>
+        <v>-0.5857596224297383</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4555,21 +4555,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8477</v>
+        <v>8104</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>256.7836204470426</v>
+        <v>263.5268279754024</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>15.35</v>
+        <v>30.85</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.43228137935697</v>
+        <v>42.08769596843214</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>4.859542496682712</v>
+        <v>24.86180437817396</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6039868791281866</v>
+        <v>0.8103441218517906</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.032593112963647</v>
+        <v>0.2639887938753532</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8070</v>
+        <v>8466</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>253.6980265672767</v>
+        <v>263.2449854096388</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>50.2</v>
+        <v>15.6</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.55543318497519</v>
+        <v>39.70238978916358</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.30898713716582</v>
+        <v>27.96885357259234</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6815760809489061</v>
+        <v>0.7386946250062111</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.2536241419014088</v>
+        <v>-0.036772795835992</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8476</v>
+        <v>8091</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>253.5472705193348</v>
+        <v>258.0575571367409</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>19.4</v>
+        <v>217.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>38.18146236886621</v>
+        <v>41.80763722868097</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11.45401971149887</v>
+        <v>15.22100864734231</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.8774532042751946</v>
+        <v>0.9696094029314486</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0189550848108573</v>
+        <v>0.539293016077921</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8121</v>
+        <v>8114</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>253.2463172799687</v>
+        <v>256.9103929573737</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>27.9</v>
+        <v>192</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>38.35394364952279</v>
+        <v>39.67616510207331</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>28.15476189992644</v>
+        <v>15.12409263051949</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.9611826960929812</v>
+        <v>0.6430788762410677</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4288084425843239</v>
+        <v>-1.461033813626115</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8341</v>
+        <v>8477</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>251.8527506676196</v>
+        <v>256.7836204470426</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>15.35</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.40681531897709</v>
+        <v>48.43228142014746</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.37080768327028</v>
+        <v>4.859542482611092</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.529901847610283</v>
+        <v>0.6039868791281866</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0353781236012127</v>
+        <v>-0.032593112963647</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8092</v>
+        <v>8070</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>250.6529947491484</v>
+        <v>253.6980265672768</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>13</v>
+        <v>50.2</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.37313685969804</v>
+        <v>51.55543323683233</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.37188932481354</v>
+        <v>17.30898713716582</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6703072818144172</v>
+        <v>0.6815760809489061</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1048761353017111</v>
+        <v>0.2536241417964688</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8404</v>
+        <v>8476</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>248.4430492434321</v>
+        <v>253.5472705193348</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>16.25</v>
+        <v>19.4</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.75043950329373</v>
+        <v>38.18146230410198</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.31237562894328</v>
+        <v>11.45401969310139</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.464644175283131</v>
+        <v>0.8774532042751946</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0333522981887327</v>
+        <v>0.0189550848585561</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8455</v>
+        <v>8121</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>247.8411405483393</v>
+        <v>253.2463172799687</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>22.7</v>
+        <v>27.9</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.70557946947869</v>
+        <v>38.35394370317196</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.48686241246959</v>
+        <v>28.15476192540119</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.298286006651317</v>
+        <v>0.9611826960929812</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.8488620769498678</v>
+        <v>0.4288084425080063</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8383</v>
+        <v>8341</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>246.8557893062363</v>
+        <v>251.8527506676196</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>66</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.55837365030885</v>
+        <v>45.40681535159489</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.62145264516993</v>
+        <v>11.37080776435642</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4033060644057629</v>
+        <v>1.529901847610283</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.2585120380282486</v>
+        <v>0.0353781234485784</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8472</v>
+        <v>8045</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>246.3655620927397</v>
+        <v>251.6266952484096</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>65</v>
+        <v>52.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>32.26722297670743</v>
+        <v>45.07160059869256</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>17.7243676311584</v>
+        <v>13.13261311999954</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.331317022556557</v>
+        <v>0.444508443910401</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0421788912100189</v>
+        <v>0.341187751961002</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8466</v>
+        <v>8092</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>243.2449854096387</v>
+        <v>250.6529947491484</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>15.6</v>
+        <v>13</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.70238977982864</v>
+        <v>46.37313700318318</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>27.96885360850301</v>
+        <v>19.37188935354102</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7386946250062111</v>
+        <v>0.6703072818144172</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0367727957692144</v>
+        <v>0.1048761352444721</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8499</v>
+        <v>8210</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>241.3357065993582</v>
+        <v>248.6400165156093</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>260</v>
+        <v>969</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45.91632273301319</v>
+        <v>41.49586129123605</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.06026531674546</v>
+        <v>16.98765835551109</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.80436037359639</v>
+        <v>0.6768379287720402</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>1.579901933141118</v>
+        <v>3.649158602977039</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8076</v>
+        <v>8455</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>239.9645507655709</v>
+        <v>247.8411405483393</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.58427811837835</v>
+        <v>49.7055794707784</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7.746161625645982</v>
+        <v>14.48686245237132</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.009355867631746</v>
+        <v>1.298286006651317</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0450955960269238</v>
+        <v>-0.8488620769880266</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8102</v>
+        <v>8383</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>238.8897421188802</v>
+        <v>246.8557893062363</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>67.2</v>
+        <v>66</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>50.9467170615356</v>
+        <v>44.55837365425564</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>9.935418757280948</v>
+        <v>12.62145267008102</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.1107578312919903</v>
+        <v>0.4033060644057629</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.6238686596440202</v>
+        <v>-0.2585120381427266</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8074</v>
+        <v>8472</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>237.1685523835379</v>
+        <v>246.3655620927397</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>55.9</v>
+        <v>65</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.78029708277396</v>
+        <v>32.26722210195616</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.39254011621768</v>
+        <v>17.72436763002194</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.951584795089903</v>
+        <v>1.331317022556557</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.5989445746750641</v>
+        <v>-0.0421788913817269</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8183</v>
+        <v>8112</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>233.6959268669072</v>
+        <v>246.1905856556352</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>28.95</v>
+        <v>90.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>42.35710778879766</v>
+        <v>49.47077885865002</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>20.2152115894543</v>
+        <v>11.52581199008317</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.204967525909645</v>
+        <v>0.3179246151727883</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0636061267933886</v>
+        <v>-0.4005302061571532</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8277</v>
+        <v>8499</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>233.1423245564845</v>
+        <v>241.3357065993582</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>260</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>45.44449037940717</v>
+        <v>45.91632284824701</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9.47638107148183</v>
+        <v>14.06026534177805</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.587679189820949</v>
+        <v>1.80436037359639</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0394918617695921</v>
+        <v>1.579901933713464</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8047</v>
+        <v>8076</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>232.6575257297658</v>
+        <v>239.964550765571</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>44</v>
+        <v>23.2</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.51797461804424</v>
+        <v>44.58427824885096</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9.135626292962742</v>
+        <v>7.746161690954503</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.267085986039733</v>
+        <v>1.009355867631746</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3698324518551481</v>
+        <v>0.0450955960173838</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8088</v>
+        <v>8183</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>227.9021355920053</v>
+        <v>233.6959268669072</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>45.25</v>
+        <v>28.95</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>40.09558724488603</v>
+        <v>42.35710785097933</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.49046274761138</v>
+        <v>20.21521162986592</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3403956814742785</v>
+        <v>1.204967525909645</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1845481828358766</v>
+        <v>0.06360612668845191</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>9136</v>
+        <v>8277</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>227.3203968826019</v>
+        <v>233.1423245564845</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>11.3</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45.9734327257277</v>
+        <v>45.44449009128591</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>10.44333413438402</v>
+        <v>9.476381230986084</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.198697433648607</v>
+        <v>1.587679189820949</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0529943425774822</v>
+        <v>0.0394918619489396</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8087</v>
+        <v>8047</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>211.6755217447525</v>
+        <v>232.6575257297658</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.81117052183085</v>
+        <v>43.51797462545662</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>7.231341469455845</v>
+        <v>9.135626377008954</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7123011070354992</v>
+        <v>0.267085986039733</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0770649708253368</v>
+        <v>-0.3698324518933099</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>9802</v>
+        <v>8088</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>205.7106098990532</v>
+        <v>227.9021355920055</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>71.5</v>
+        <v>45.25</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.75115049532609</v>
+        <v>40.09558720583773</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9.99671487218184</v>
+        <v>13.49046274761138</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2354982235889754</v>
+        <v>0.3403956814742785</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.1512200156637807</v>
+        <v>0.1845481828931157</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8291</v>
+        <v>9136</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>204.2516982644125</v>
+        <v>227.3203968826019</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>34.05</v>
+        <v>11.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.41166501570565</v>
+        <v>45.97343272214782</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12.00818767533356</v>
+        <v>10.44333413455807</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.1152027418604685</v>
+        <v>0.198697433648607</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1280511656889371</v>
+        <v>0.0529943425793902</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8064</v>
+        <v>8087</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>201.0713391728775</v>
+        <v>211.6755217447525</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>43.94722877768182</v>
+        <v>50.81117051107259</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.9821532924849</v>
+        <v>7.231341484495458</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7587928486163047</v>
+        <v>0.7123011070354992</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>1.266201325324602</v>
+        <v>0.0770649708157999</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8049</v>
+        <v>8291</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>195.5771425311047</v>
+        <v>204.2516982644125</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>24.55</v>
+        <v>34.05</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>35.27056021261514</v>
+        <v>44.41126383216361</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>22.32933805284599</v>
+        <v>12.00794038354543</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4650396046603434</v>
+        <v>0.1152027418604685</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.056321113994042</v>
+        <v>0.1280533946491124</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8487</v>
+        <v>8049</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>186.3041549605039</v>
+        <v>195.5771425311046</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>70.5</v>
+        <v>24.55</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>32.11007006141747</v>
+        <v>35.27056023779774</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.287592530908</v>
+        <v>22.32933803772241</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.499961167310642</v>
+        <v>0.4650396046603434</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1193748317959206</v>
+        <v>-0.0563211140035806</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8201</v>
+        <v>8487</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>177.5565937424728</v>
+        <v>186.3041549605039</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>11.9</v>
+        <v>70.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>47.77143866879238</v>
+        <v>32.11007003398838</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>19.79056312259976</v>
+        <v>14.28759254629668</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.7977021511209127</v>
+        <v>1.499961167310642</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0459689773131639</v>
+        <v>0.1193748318531515</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8045</v>
+        <v>8201</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>176.6266952484095</v>
+        <v>177.5565937424728</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>52.3</v>
+        <v>11.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.071600523196</v>
+        <v>47.77143862369926</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.1326130690561</v>
+        <v>19.79056313148937</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.444508443910401</v>
+        <v>0.7977021511209127</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.3411877521327204</v>
+        <v>0.0459689773322425</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>37.81731016445506</v>
+        <v>37.81731045264948</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.64669169936547</v>
+        <v>22.6466916634818</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.2668399855906407</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1269051915870852</v>
+        <v>-0.1269051916347848</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.8289681148848</v>
+        <v>42.82896830427237</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>19.19849279725855</v>
+        <v>19.19849271770232</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.8755710704495935</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0520745926898357</v>
+        <v>0.0520745925658167</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.70042300385607</v>
+        <v>39.70042308347345</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>8.258584192135221</v>
+        <v>8.258584167289499</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>1.146702918617726</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.543776415313</v>
+        <v>38.54377647036524</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.85392103852949</v>
+        <v>13.8539210964584</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.6281747088912787</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0115510031266532</v>
+        <v>0.0115510030694144</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>38.1652444507821</v>
+        <v>38.16524406626401</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>19.5149433149854</v>
+        <v>19.5149432747629</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.7148201278782731</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0582084294451386</v>
+        <v>0.0582084297599501</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.11415786617395</v>
+        <v>43.11415786935476</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.48496331474489</v>
+        <v>13.48496353150262</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.5906794798742582</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.2964150128706631</v>
+        <v>0.2964150128420448</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>147.5305617770572</v>
+        <v>147.5305617770573</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>92.2</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>36.34863180948401</v>
+        <v>36.34863182722825</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>10.9491383300265</v>
+        <v>10.94913834251844</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.4663089352198228</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.2419956537886172</v>
+        <v>-0.241995653979405</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>147.3520665610352</v>
+        <v>147.352066561035</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>141</v>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>38.97467389143252</v>
+        <v>38.97467374267615</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.48055222982288</v>
+        <v>12.48055225202193</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.9227796526506492</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.1432905301016451</v>
+        <v>0.1432905310556118</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>143.3516304920141</v>
+        <v>143.3516304920143</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>24.15</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>31.8001706869124</v>
+        <v>31.80017070416177</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.39128883051186</v>
+        <v>15.39128894483975</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.6376458399086973</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1543074622293653</v>
+        <v>-0.154307462286602</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>51.4377179056516</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>6.415265999562456</v>
+        <v>6.415265999562454</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.6005109337642062</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1023767185356859</v>
+        <v>0.1023767184975272</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.83602645694071</v>
+        <v>44.83602644772941</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.42183614835106</v>
+        <v>17.42183611027723</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.4029593489241321</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.4884453167464399</v>
+        <v>-0.4884453167655185</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>126.3359066515468</v>
+        <v>126.3359066515466</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>156.5</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>35.1286215662392</v>
+        <v>35.12862144988802</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>19.31863318482558</v>
+        <v>19.31863315722553</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.229661079545245</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0309852578497054</v>
+        <v>-0.0309852573727269</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>92.85880214246484</v>
+        <v>92.85880214246448</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>17.7</v>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>41.19045531884316</v>
+        <v>41.19045546517767</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>9.091414746446052</v>
+        <v>9.091414793139251</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>1.076336900023129</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0513963514550739</v>
+        <v>0.0513963512547404</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
